--- a/outputs_xlsx_solution/test2.2-wide.xlsx
+++ b/outputs_xlsx_solution/test2.2-wide.xlsx
@@ -62,15 +62,18 @@
     <t>bne X1, X0, 4</t>
   </si>
   <si>
-    <t>IS/EX</t>
-  </si>
-  <si>
-    <t>WB/CT</t>
-  </si>
-  <si>
     <t>EX</t>
   </si>
   <si>
+    <t>IS</t>
+  </si>
+  <si>
+    <t>WB</t>
+  </si>
+  <si>
+    <t>CT</t>
+  </si>
+  <si>
     <t>[Legend]</t>
   </si>
   <si>
@@ -80,13 +83,34 @@
     <t>Instruction Decode</t>
   </si>
   <si>
-    <t>Add to Issue Queue/Execute (if instruction is ready, it can start executing in the same cycle it is added to issue queue)</t>
-  </si>
-  <si>
-    <t>Execute</t>
-  </si>
-  <si>
-    <t>Write Back/Commit (instruction can be committed on the same cycle it writes back)</t>
+    <t>Add to Issue Queue</t>
+  </si>
+  <si>
+    <t>Execute (instruction can execute on the same cycle as it is added to the issue queue, if it is ready)</t>
+  </si>
+  <si>
+    <t>Write Back</t>
+  </si>
+  <si>
+    <t>Commit (instruction can commit on the same cycle as write back, if at the head)</t>
+  </si>
+  <si>
+    <t>RS Stall</t>
+  </si>
+  <si>
+    <t>Reservation Station Stall (stalled because reservation stations are full)</t>
+  </si>
+  <si>
+    <t>ROB Stall</t>
+  </si>
+  <si>
+    <t>Reorder Buffer Stall (stalled because the ROB is full)</t>
+  </si>
+  <si>
+    <t>CDB Stall</t>
+  </si>
+  <si>
+    <t>Common Data Bus Stall (stalled because the CDB bandwidth is saturated)</t>
   </si>
 </sst>
 </file>
@@ -513,7 +537,7 @@
         <v>9</v>
       </c>
       <c r="G2" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
     </row>
     <row r="3">
@@ -533,13 +557,13 @@
         <v>7</v>
       </c>
       <c r="F3" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="G3" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="H3" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
     </row>
     <row r="4">
@@ -559,13 +583,13 @@
         <v>7</v>
       </c>
       <c r="G4" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="H4" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="I4" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
     </row>
     <row r="5">
@@ -588,35 +612,38 @@
         <v>9</v>
       </c>
       <c r="L5" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
     </row>
     <row r="6">
       <c r="A6">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="B6">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="C6" t="s">
-        <v>6</v>
+        <v>8</v>
+      </c>
+      <c r="I6" t="s">
+        <v>5</v>
       </c>
       <c r="J6" t="s">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="K6" t="s">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="L6" t="s">
         <v>9</v>
       </c>
       <c r="M6" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
     </row>
     <row r="7">
       <c r="A7">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="B7">
         <v>4</v>
@@ -624,111 +651,210 @@
       <c r="C7" t="s">
         <v>6</v>
       </c>
+      <c r="J7" t="s">
+        <v>5</v>
+      </c>
       <c r="K7" t="s">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="L7" t="s">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="M7" t="s">
-        <v>9</v>
-      </c>
-      <c r="N7" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
     </row>
     <row r="8">
       <c r="A8">
+        <v>7</v>
+      </c>
+      <c r="B8">
+        <v>8</v>
+      </c>
+      <c r="C8" t="s">
+        <v>8</v>
+      </c>
+      <c r="J8" t="s">
+        <v>5</v>
+      </c>
+      <c r="K8" t="s">
+        <v>7</v>
+      </c>
+      <c r="L8" t="s">
         <v>10</v>
       </c>
-      <c r="B8">
-        <v>4</v>
-      </c>
-      <c r="C8" t="s">
-        <v>6</v>
-      </c>
-      <c r="L8" t="s">
-        <v>5</v>
-      </c>
       <c r="M8" t="s">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="N8" t="s">
-        <v>9</v>
-      </c>
-      <c r="O8" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
     </row>
     <row r="9">
       <c r="A9">
+        <v>8</v>
+      </c>
+      <c r="B9">
+        <v>4</v>
+      </c>
+      <c r="C9" t="s">
+        <v>6</v>
+      </c>
+      <c r="K9" t="s">
+        <v>5</v>
+      </c>
+      <c r="L9" t="s">
+        <v>7</v>
+      </c>
+      <c r="M9" t="s">
+        <v>9</v>
+      </c>
+      <c r="N9" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10">
+        <v>9</v>
+      </c>
+      <c r="B10">
+        <v>8</v>
+      </c>
+      <c r="C10" t="s">
+        <v>8</v>
+      </c>
+      <c r="K10" t="s">
+        <v>5</v>
+      </c>
+      <c r="L10" t="s">
+        <v>7</v>
+      </c>
+      <c r="M10" t="s">
+        <v>10</v>
+      </c>
+      <c r="N10" t="s">
+        <v>9</v>
+      </c>
+      <c r="O10" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11">
+        <v>10</v>
+      </c>
+      <c r="B11">
+        <v>4</v>
+      </c>
+      <c r="C11" t="s">
+        <v>6</v>
+      </c>
+      <c r="L11" t="s">
+        <v>5</v>
+      </c>
+      <c r="M11" t="s">
+        <v>7</v>
+      </c>
+      <c r="N11" t="s">
+        <v>9</v>
+      </c>
+      <c r="O11" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12">
         <v>11</v>
       </c>
-      <c r="B9">
-        <v>8</v>
-      </c>
-      <c r="C9" t="s">
-        <v>8</v>
-      </c>
-      <c r="L9" t="s">
-        <v>5</v>
-      </c>
-      <c r="M9" t="s">
-        <v>7</v>
-      </c>
-      <c r="N9" t="s">
-        <v>9</v>
-      </c>
-      <c r="O9" t="s">
-        <v>11</v>
-      </c>
-      <c r="P9" t="s">
+      <c r="B12">
+        <v>8</v>
+      </c>
+      <c r="C12" t="s">
+        <v>8</v>
+      </c>
+      <c r="L12" t="s">
+        <v>5</v>
+      </c>
+      <c r="M12" t="s">
+        <v>7</v>
+      </c>
+      <c r="N12" t="s">
         <v>10</v>
       </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="s">
-        <v>5</v>
-      </c>
-      <c r="B12" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="s">
-        <v>7</v>
-      </c>
-      <c r="B13" t="s">
-        <v>14</v>
+      <c r="O12" t="s">
+        <v>9</v>
+      </c>
+      <c r="P12" t="s">
+        <v>12</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="s">
-        <v>9</v>
-      </c>
-      <c r="B14" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="s">
-        <v>11</v>
+        <v>5</v>
       </c>
       <c r="B15" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="s">
+        <v>7</v>
+      </c>
+      <c r="B16" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="s">
         <v>10</v>
       </c>
-      <c r="B16" t="s">
+      <c r="B17" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="s">
+        <v>9</v>
+      </c>
+      <c r="B18" t="s">
         <v>17</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="s">
+        <v>11</v>
+      </c>
+      <c r="B19" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="s">
+        <v>12</v>
+      </c>
+      <c r="B20" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="s">
+        <v>20</v>
+      </c>
+      <c r="B21" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="s">
+        <v>24</v>
+      </c>
+      <c r="B22" t="s">
+        <v>25</v>
       </c>
     </row>
   </sheetData>

--- a/outputs_xlsx_solution/test2.2-wide.xlsx
+++ b/outputs_xlsx_solution/test2.2-wide.xlsx
@@ -111,6 +111,12 @@
   </si>
   <si>
     <t>Common Data Bus Stall (stalled because the CDB bandwidth is saturated)</t>
+  </si>
+  <si>
+    <t>FU Stall</t>
+  </si>
+  <si>
+    <t>Functional Unit Stall (stalled because the functional unit is busy)</t>
   </si>
 </sst>
 </file>
@@ -851,10 +857,26 @@
     </row>
     <row r="22">
       <c r="A22" t="s">
+        <v>22</v>
+      </c>
+      <c r="B22" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="s">
         <v>24</v>
       </c>
-      <c r="B22" t="s">
+      <c r="B23" t="s">
         <v>25</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="s">
+        <v>26</v>
+      </c>
+      <c r="B24" t="s">
+        <v>27</v>
       </c>
     </row>
   </sheetData>
